--- a/config/docs/Scope Structure.xlsx
+++ b/config/docs/Scope Structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robhay/Developer/share_screener/config/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20921A16-A30C-1A43-B726-C437C03D52DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9AAA66-9E37-3746-BDEC-3C4D7D1FC30E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="72960" yWindow="-3860" windowWidth="38400" windowHeight="21100" xr2:uid="{952C95C7-3405-C54E-B78D-3397068AE8B3}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="146">
   <si>
     <t>Scope</t>
   </si>
@@ -319,9 +319,6 @@
  access to the above code</t>
   </si>
   <si>
-    <t>Config Groups</t>
-  </si>
-  <si>
     <t>Path</t>
   </si>
   <si>
@@ -419,6 +416,62 @@
   </si>
   <si>
     <t>websites</t>
+  </si>
+  <si>
+    <t>set_scope</t>
+  </si>
+  <si>
+    <t>Index Page</t>
+  </si>
+  <si>
+    <t>module / page__ &lt;scope &gt;</t>
+  </si>
+  <si>
+    <t>page_&lt;module&gt;</t>
+  </si>
+  <si>
+    <t>page_intraday</t>
+  </si>
+  <si>
+    <t>page_charts</t>
+  </si>
+  <si>
+    <t>page_test</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>page_research</t>
+  </si>
+  <si>
+    <t>page_screener</t>
+  </si>
+  <si>
+    <t>page_ticker_index</t>
+  </si>
+  <si>
+    <t>scope_verdicts</t>
+  </si>
+  <si>
+    <t>config_config_verdicts</t>
+  </si>
+  <si>
+    <t>Sub Module</t>
+  </si>
+  <si>
+    <t>summary</t>
+  </si>
+  <si>
+    <t>page_welcome
+page_logout
+page_login</t>
+  </si>
+  <si>
+    <t>page_volume</t>
+  </si>
+  <si>
+    <t>page_websites</t>
   </si>
 </sst>
 </file>
@@ -573,8 +626,9 @@
     </font>
     <font>
       <b/>
+      <i/>
       <sz val="16"/>
-      <color theme="0" tint="-0.34998626667073579"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -582,7 +636,7 @@
     <font>
       <b/>
       <i/>
-      <sz val="16"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -633,7 +687,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -710,6 +764,17 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -761,11 +826,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -788,12 +864,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -812,6 +882,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -830,19 +903,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -881,12 +960,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -902,16 +981,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -936,21 +1009,9 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -960,26 +1021,50 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1295,209 +1380,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14994931-7C6C-9340-B5B5-F2DD8D95EA73}">
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:BF29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" style="5" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" style="5" customWidth="1"/>
     <col min="4" max="4" width="9.1640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" style="33" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.1640625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="20" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" style="34" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="20" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="16" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="18.33203125" style="5" customWidth="1"/>
-    <col min="17" max="17" width="17.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="18.33203125" style="5" customWidth="1"/>
-    <col min="20" max="20" width="22.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="18.33203125" style="5" customWidth="1"/>
-    <col min="27" max="27" width="19" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="25.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14" style="5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="10.83203125" style="5"/>
+    <col min="14" max="14" width="16" style="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.5" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18" style="22" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18" style="22" customWidth="1"/>
+    <col min="25" max="25" width="14" style="22" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17" style="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="18.33203125" style="5" customWidth="1"/>
+    <col min="33" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="26" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:32" ht="26" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-    </row>
-    <row r="3" spans="1:30" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E3" s="47" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="8" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="68"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+    </row>
+    <row r="3" spans="1:32" s="57" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="E3" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="58" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="60"/>
+      <c r="K3" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="73"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="J3" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="59"/>
-      <c r="L3" s="39" t="s">
+      <c r="P3" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q3" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="60"/>
+      <c r="S3" s="58" t="s">
+        <v>124</v>
+      </c>
+      <c r="T3" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="U3" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="V3" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="W3" s="73"/>
+      <c r="X3" s="73"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA3" s="60"/>
+      <c r="AB3" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD3" s="58" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="E4" s="74" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="59"/>
-      <c r="N3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V3" s="1" t="s">
+      <c r="M4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="51" t="s">
+        <v>6</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y4" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z4" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="W3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AA4" s="51" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" s="61" customFormat="1" ht="21" x14ac:dyDescent="0.2">
-      <c r="E4" s="68" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="62"/>
-      <c r="H4" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="I4" s="63" t="s">
-        <v>122</v>
-      </c>
-      <c r="J4" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="65"/>
-      <c r="L4" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="M4" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="N4" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" s="63" t="s">
-        <v>123</v>
-      </c>
-      <c r="P4" s="63" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q4" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="63" t="s">
-        <v>125</v>
-      </c>
-      <c r="S4" s="63" t="s">
-        <v>126</v>
-      </c>
-      <c r="T4" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="U4" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="V4" s="63" t="s">
-        <v>30</v>
-      </c>
-      <c r="W4" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="X4" s="63" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y4" s="63" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z4" s="52"/>
-      <c r="AA4" s="67"/>
-      <c r="AB4" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC4" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD4" s="52" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+    </row>
+    <row r="5" spans="1:32" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.2">
       <c r="E5" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -1507,33 +1573,31 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="49" t="s">
-        <v>81</v>
-      </c>
+      <c r="U5" s="1"/>
+      <c r="V5" s="51"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="51"/>
+      <c r="AA5" s="51"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="E6" s="47" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="J6" s="6" t="s">
         <v>27</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>27</v>
@@ -1549,13 +1613,11 @@
       <c r="Q6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="R6" s="4"/>
+      <c r="R6" s="6"/>
       <c r="S6" s="4"/>
-      <c r="T6" s="6" t="s">
+      <c r="T6" s="4"/>
+      <c r="U6" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="U6" s="48" t="s">
-        <v>25</v>
       </c>
       <c r="V6" s="6" t="s">
         <v>27</v>
@@ -1563,913 +1625,1180 @@
       <c r="W6" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="6" t="s">
+      <c r="X6" s="48"/>
+      <c r="Y6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC6" s="6" t="s">
+      <c r="Z6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AD6" s="6" t="s">
+      <c r="AA6" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB6" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="E7" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>100</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="K7" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="N7" s="6"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="4"/>
-      <c r="R7" s="2"/>
+      <c r="R7" s="4"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="4"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="K8" s="25"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
-      <c r="U8" s="46"/>
-      <c r="V8" s="15"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="45"/>
-      <c r="AD8" s="50"/>
-    </row>
-    <row r="9" spans="1:30" s="7" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="49"/>
+      <c r="AC8" s="46"/>
+      <c r="AD8" s="46"/>
+    </row>
+    <row r="9" spans="1:32" s="7" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="26" t="s">
+      <c r="F9" s="38"/>
+      <c r="G9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="70"/>
-      <c r="L9" s="16" t="s">
+      <c r="J9" s="64"/>
+      <c r="K9" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="N9" s="16" t="s">
+      <c r="M9" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="16" t="s">
+      <c r="O9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="16" t="s">
+      <c r="R9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="U9" s="60" t="s">
+      <c r="V9" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="W9" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="X9" s="72" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y9" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z9" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="W9" s="17" t="s">
+      <c r="AA9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB9" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="11"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="58"/>
-      <c r="AB9" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD9" s="16" t="s">
+      <c r="AC9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD9" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" s="7" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="38"/>
+      <c r="G10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="65"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="V10" s="67"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="67"/>
+      <c r="Y10" s="67"/>
+      <c r="Z10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA10" s="15" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" s="7" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="71"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="U10" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="V10" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="W10" s="17" t="s">
+      <c r="AB10" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="11"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="58"/>
-      <c r="AB10" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC10" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD10" s="16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" s="3" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="28" t="s">
+      <c r="AC10" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD10" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" s="3" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="29" t="s">
         <v>88</v>
       </c>
       <c r="C11" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="16" t="s">
+      <c r="F11" s="32"/>
+      <c r="G11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="62" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="62"/>
+      <c r="K11" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="69"/>
-      <c r="L11" s="16" t="s">
+      <c r="L11" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="N11" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="V11" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="W11" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="X11" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y11" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z11" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD11" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" s="3" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="19"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="32"/>
+      <c r="G12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="62"/>
+      <c r="K12" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="L12" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="M12" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="N11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="U11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="V11" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="11"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB11" s="16" t="s">
+      <c r="N12" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U12" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="V12" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="W12" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="X12" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="AC11" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD11" s="16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" s="3" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="20"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="27" t="s">
+      <c r="Y12" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z12" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA12" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB12" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD12" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" s="3" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="W13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z13" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD13" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B14" s="30"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J12" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="K12" s="69"/>
-      <c r="L12" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="U12" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="V12" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="W12" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB12" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC12" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD12" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" s="3" customFormat="1" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="27" t="s">
+      <c r="E14" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="39"/>
+      <c r="G14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="U14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z14" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD14" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" s="3" customFormat="1" ht="54" x14ac:dyDescent="0.2">
+      <c r="B15" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="38"/>
-      <c r="G13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="V13" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD13" s="14" t="s">
+      <c r="E15" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="39"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="62"/>
+      <c r="K15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O15" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R15" s="70" t="s">
+        <v>134</v>
+      </c>
+      <c r="S15" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="T15" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="U15" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="V15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB15" s="75" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC15" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD15" s="63" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="C16" s="21"/>
+      <c r="AE16" s="5"/>
+      <c r="AF16" s="5"/>
+    </row>
+    <row r="17" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="C17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE17" s="5"/>
+      <c r="AF17" s="5"/>
+    </row>
+    <row r="18" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="J18" s="37"/>
+      <c r="K18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="L18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="N18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="O18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="V18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="W18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="X18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
+    </row>
+    <row r="19" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="30"/>
+      <c r="C19" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA19" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B14" s="29"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="38"/>
-      <c r="G14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="V14" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD14" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C16" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13" t="s">
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="5"/>
+    </row>
+    <row r="20" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="30"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="K17" s="36"/>
-      <c r="L17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="M17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="N17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="U17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="V17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="W17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC17" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD17" s="43" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="29"/>
-      <c r="C18" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="X20" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA20" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="9"/>
+      <c r="AD20" s="9"/>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="5"/>
+    </row>
+    <row r="21" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="30"/>
+      <c r="C21" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="19" t="s">
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="11"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="29"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="13" t="s">
+      <c r="J21" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="9"/>
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
+      <c r="AD21" s="9"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+    </row>
+    <row r="22" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="30"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="18" t="s">
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="18" t="s">
+      <c r="J22" s="43"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="V19" s="18" t="s">
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="5"/>
+      <c r="AF22" s="5"/>
+    </row>
+    <row r="23" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="30"/>
+      <c r="C23" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="18" t="s">
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="18" t="s">
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="5"/>
+      <c r="AF23" s="5"/>
+    </row>
+    <row r="24" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="30"/>
+      <c r="C24" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="20" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="29"/>
-      <c r="C20" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="11"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-    </row>
-    <row r="21" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="29"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="13" t="s">
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="9"/>
+      <c r="AC24" s="9"/>
+      <c r="AD24" s="9"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="5"/>
+    </row>
+    <row r="25" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="30"/>
+      <c r="C25" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="42" t="s">
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="K21" s="42"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="18" t="s">
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
+      <c r="AC25" s="9"/>
+      <c r="AD25" s="9"/>
+      <c r="AE25" s="5"/>
+      <c r="AF25" s="5"/>
+    </row>
+    <row r="26" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="30"/>
+      <c r="C26" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="18" t="s">
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="5"/>
+      <c r="AF26" s="5"/>
+    </row>
+    <row r="27" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="30"/>
+      <c r="C27" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="11"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="11"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="11"/>
-      <c r="AD21" s="11"/>
-    </row>
-    <row r="22" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="29"/>
-      <c r="C22" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="5"/>
+      <c r="AF27" s="5"/>
+    </row>
+    <row r="28" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="30"/>
+      <c r="C28" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="18" t="s">
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="5"/>
+      <c r="AF28" s="5"/>
+    </row>
+    <row r="29" spans="2:32" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="30"/>
+      <c r="C29" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="11"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="11"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
-    </row>
-    <row r="23" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="29"/>
-      <c r="C23" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="V23" s="11"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="11"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="11"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-    </row>
-    <row r="24" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="29"/>
-      <c r="C24" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="11"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="11"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="11"/>
-      <c r="AD24" s="11"/>
-    </row>
-    <row r="25" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="29"/>
-      <c r="C25" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="11"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="11"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="11"/>
-      <c r="AD25" s="11"/>
-    </row>
-    <row r="26" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="29"/>
-      <c r="C26" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="U26" s="11"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="11"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="11"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="11"/>
-      <c r="AD26" s="11"/>
-    </row>
-    <row r="27" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="29"/>
-      <c r="C27" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="R27" s="11"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="11"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="11"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="11"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="11"/>
-      <c r="AD27" s="11"/>
-    </row>
-    <row r="28" spans="2:30" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="29"/>
-      <c r="C28" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="V28" s="11"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="11"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="11"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="11"/>
-      <c r="AD28" s="11"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
+      <c r="AD29" s="9"/>
+      <c r="AE29" s="5"/>
+      <c r="AF29" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="J9:K10"/>
-    <mergeCell ref="L3:M3"/>
+  <mergeCells count="28">
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="Q9:Q10"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B17:B28"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="B18:B29"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="I3:J3"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
@@ -2489,57 +2818,57 @@
     <col min="4" max="5" width="33.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:5" s="53" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="52" t="s">
+    <row r="4" spans="2:5" s="52" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="51" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="52" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="54" t="s">
+      <c r="D7" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C8" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D8" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="54" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="54" t="s">
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C9" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="54" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B9" s="54" t="s">
+      <c r="D9" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="E9" s="53" t="s">
         <v>119</v>
-      </c>
-      <c r="D9" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" s="54" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
